--- a/output1.xlsx
+++ b/output1.xlsx
@@ -431,19 +431,19 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>col 1</t>
+          <t>col_1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>col 2</t>
+          <t>col_2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>row 1</t>
+          <t>row_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,16 +451,14 @@
           <t>a</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>row 2</t>
+          <t>row_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -468,10 +466,8 @@
           <t>c</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
+      <c r="C3" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
